--- a/output/roomself_excel/3842.xlsx
+++ b/output/roomself_excel/3842.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34668</v>
+        <v>85008</v>
       </c>
       <c r="D2" t="n">
-        <v>1504</v>
+        <v>2356</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F2" t="n">
-        <v>203</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>109782</v>
+        <v>373974</v>
       </c>
       <c r="D3" t="n">
-        <v>2780</v>
+        <v>5832</v>
       </c>
       <c r="E3" t="n">
-        <v>555</v>
+        <v>994</v>
       </c>
       <c r="F3" t="n">
-        <v>215</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>625385</v>
+        <v>109782</v>
       </c>
       <c r="D4" t="n">
-        <v>10464</v>
+        <v>2780</v>
       </c>
       <c r="E4" t="n">
-        <v>1002</v>
+        <v>288</v>
       </c>
       <c r="F4" t="n">
-        <v>994</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17433</v>
+        <v>118210</v>
       </c>
       <c r="D6" t="n">
-        <v>1064</v>
+        <v>2980</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>265</v>
       </c>
       <c r="F6" t="n">
         <v>41</v>
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>118210</v>
+        <v>111758</v>
       </c>
       <c r="D7" t="n">
-        <v>2980</v>
+        <v>2676</v>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="F7" t="n">
-        <v>277</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -598,14 +598,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16263</v>
+        <v>15340</v>
       </c>
       <c r="D8" t="n">
-        <v>1024</v>
+        <v>992</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25670</v>
+        <v>50588</v>
       </c>
       <c r="D9" t="n">
-        <v>1284</v>
+        <v>2004</v>
       </c>
       <c r="E9" t="n">
-        <v>170</v>
+        <v>229</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31047</v>
+        <v>31768</v>
       </c>
       <c r="D10" t="n">
-        <v>1472</v>
+        <v>1444</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>148564</v>
+        <v>166403</v>
       </c>
       <c r="D11" t="n">
-        <v>3588</v>
+        <v>4408</v>
       </c>
       <c r="E11" t="n">
-        <v>597</v>
+        <v>207</v>
       </c>
       <c r="F11" t="n">
-        <v>251</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19320</v>
+        <v>34668</v>
       </c>
       <c r="D12" t="n">
-        <v>1124</v>
+        <v>1504</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18000</v>
+        <v>17433</v>
       </c>
       <c r="D13" t="n">
-        <v>1080</v>
+        <v>1064</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>111758</v>
+        <v>16263</v>
       </c>
       <c r="D14" t="n">
-        <v>2676</v>
+        <v>1024</v>
       </c>
       <c r="E14" t="n">
-        <v>323</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -752,14 +752,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15340</v>
+        <v>31047</v>
       </c>
       <c r="D15" t="n">
-        <v>992</v>
+        <v>1472</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>56232</v>
+        <v>68224</v>
       </c>
       <c r="D16" t="n">
-        <v>1928</v>
+        <v>2144</v>
       </c>
       <c r="E16" t="n">
-        <v>325</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50588</v>
+        <v>19320</v>
       </c>
       <c r="D17" t="n">
-        <v>2004</v>
+        <v>1124</v>
       </c>
       <c r="E17" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,86 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31768</v>
+        <v>18000</v>
       </c>
       <c r="D18" t="n">
-        <v>1444</v>
+        <v>1080</v>
       </c>
       <c r="E18" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25670</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1284</v>
+      </c>
+      <c r="E19" t="n">
+        <v>170</v>
+      </c>
+      <c r="F19" t="n">
         <v>41</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>80340</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2276</v>
+      </c>
+      <c r="E20" t="n">
+        <v>260</v>
+      </c>
+      <c r="F20" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>56232</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1928</v>
+      </c>
+      <c r="E21" t="n">
+        <v>325</v>
+      </c>
+      <c r="F21" t="n">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3842.xlsx
+++ b/output/roomself_excel/3842.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2356</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>253</v>
       </c>
-      <c r="F2" t="n">
-        <v>41</v>
-      </c>
+      <c r="G2" t="n">
+        <v>41</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>5832</v>
       </c>
-      <c r="E3" t="n">
-        <v>994</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>544</v>
-      </c>
+        <v>851</v>
+      </c>
+      <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +555,20 @@
       <c r="D4" t="n">
         <v>2780</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>288</v>
       </c>
-      <c r="F4" t="n">
-        <v>41</v>
-      </c>
+      <c r="G4" t="n">
+        <v>41</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +585,20 @@
       <c r="D5" t="n">
         <v>2632</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>358</v>
       </c>
-      <c r="F5" t="n">
-        <v>41</v>
-      </c>
+      <c r="G5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +615,27 @@
       <c r="D6" t="n">
         <v>2980</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>265</v>
       </c>
-      <c r="F6" t="n">
-        <v>41</v>
+      <c r="G6" t="n">
+        <v>41</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>422</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -585,10 +653,26 @@
       <c r="D7" t="n">
         <v>2676</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>346</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>323</v>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>41</v>
       </c>
     </row>
@@ -607,12 +691,12 @@
       <c r="D8" t="n">
         <v>992</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +713,20 @@
       <c r="D9" t="n">
         <v>2004</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>229</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>53</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +743,20 @@
       <c r="D10" t="n">
         <v>1444</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>152</v>
       </c>
-      <c r="F10" t="n">
-        <v>41</v>
-      </c>
+      <c r="G10" t="n">
+        <v>41</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>4408</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>207</v>
       </c>
-      <c r="F11" t="n">
-        <v>41</v>
-      </c>
+      <c r="G11" t="n">
+        <v>41</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +803,27 @@
       <c r="D12" t="n">
         <v>1504</v>
       </c>
-      <c r="E12" t="n">
-        <v>255</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>203</v>
+        <v>214</v>
+      </c>
+      <c r="G12" t="n">
+        <v>41</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>162</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +841,20 @@
       <c r="D13" t="n">
         <v>1064</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>117</v>
       </c>
-      <c r="F13" t="n">
-        <v>41</v>
-      </c>
+      <c r="G13" t="n">
+        <v>41</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +871,12 @@
       <c r="D14" t="n">
         <v>1024</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +893,12 @@
       <c r="D15" t="n">
         <v>1472</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +915,12 @@
       <c r="D16" t="n">
         <v>2144</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +937,12 @@
       <c r="D17" t="n">
         <v>1124</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +959,20 @@
       <c r="D18" t="n">
         <v>1080</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +989,20 @@
       <c r="D19" t="n">
         <v>1284</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>170</v>
       </c>
-      <c r="F19" t="n">
-        <v>41</v>
-      </c>
+      <c r="G19" t="n">
+        <v>41</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1019,20 @@
       <c r="D20" t="n">
         <v>2276</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>260</v>
       </c>
-      <c r="F20" t="n">
-        <v>41</v>
-      </c>
+      <c r="G20" t="n">
+        <v>41</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1049,27 @@
       <c r="D21" t="n">
         <v>1928</v>
       </c>
-      <c r="E21" t="n">
-        <v>325</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>239</v>
+        <v>284</v>
+      </c>
+      <c r="G21" t="n">
+        <v>41</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>198</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3842.xlsx
+++ b/output/roomself_excel/3842.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +549,26 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>112</v>
+      </c>
+      <c r="N2" t="n">
+        <v>41</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -539,6 +599,38 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>94</v>
+      </c>
+      <c r="N3" t="n">
+        <v>41</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>438</v>
+      </c>
+      <c r="R3" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -569,6 +661,26 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>140</v>
+      </c>
+      <c r="N4" t="n">
+        <v>41</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -599,6 +711,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>138</v>
+      </c>
+      <c r="N5" t="n">
+        <v>41</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -637,6 +769,26 @@
       <c r="J6" t="n">
         <v>39</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>144</v>
+      </c>
+      <c r="N6" t="n">
+        <v>41</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -675,6 +827,26 @@
       <c r="J7" t="n">
         <v>41</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>142</v>
+      </c>
+      <c r="N7" t="n">
+        <v>41</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -697,6 +869,14 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -727,6 +907,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -757,6 +945,26 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>41</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -787,6 +995,26 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>93</v>
+      </c>
+      <c r="N11" t="n">
+        <v>41</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -825,6 +1053,14 @@
       <c r="J12" t="n">
         <v>41</v>
       </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -855,6 +1091,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -877,6 +1121,14 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -899,6 +1151,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -921,6 +1181,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -943,6 +1211,14 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -973,6 +1249,14 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1003,6 +1287,26 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>90</v>
+      </c>
+      <c r="N19" t="n">
+        <v>41</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1033,6 +1337,26 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>94</v>
+      </c>
+      <c r="N20" t="n">
+        <v>41</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1071,6 +1395,26 @@
       <c r="J21" t="n">
         <v>41</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>53</v>
+      </c>
+      <c r="N21" t="n">
+        <v>41</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
